--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -392,7 +392,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -800,7 +800,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="66.87109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
